--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -15260,10 +15260,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132621909</v>
+        <v>132621900</v>
       </c>
       <c r="B138" t="n">
-        <v>81318</v>
+        <v>79091</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15271,21 +15271,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>410246</v>
+        <v>410323</v>
       </c>
       <c r="R138" t="n">
-        <v>6741556</v>
+        <v>6741612</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15357,10 +15357,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132621910</v>
+        <v>132621921</v>
       </c>
       <c r="B139" t="n">
-        <v>81318</v>
+        <v>91932</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15368,21 +15368,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>410252</v>
+        <v>410323</v>
       </c>
       <c r="R139" t="n">
-        <v>6741547</v>
+        <v>6741552</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15454,10 +15454,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132621921</v>
+        <v>132621909</v>
       </c>
       <c r="B140" t="n">
-        <v>91932</v>
+        <v>81318</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15465,21 +15465,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>410323</v>
+        <v>410246</v>
       </c>
       <c r="R140" t="n">
-        <v>6741552</v>
+        <v>6741556</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132621858</v>
+        <v>132621910</v>
       </c>
       <c r="B141" t="n">
-        <v>79365</v>
+        <v>81318</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410236</v>
+        <v>410252</v>
       </c>
       <c r="R141" t="n">
-        <v>6741532</v>
+        <v>6741547</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15641,17 +15641,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132621900</v>
+        <v>132621858</v>
       </c>
       <c r="B142" t="n">
-        <v>79091</v>
+        <v>79365</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15659,21 +15659,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>410323</v>
+        <v>410236</v>
       </c>
       <c r="R142" t="n">
-        <v>6741612</v>
+        <v>6741532</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132621906</v>
+        <v>132621870</v>
       </c>
       <c r="B147" t="n">
-        <v>81318</v>
+        <v>79952</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410318</v>
+        <v>410249</v>
       </c>
       <c r="R147" t="n">
-        <v>6741598</v>
+        <v>6741544</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132621888</v>
+        <v>132621865</v>
       </c>
       <c r="B148" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16241,21 +16241,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410330</v>
+        <v>410608</v>
       </c>
       <c r="R148" t="n">
-        <v>6741585</v>
+        <v>6741559</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16320,17 +16320,17 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132621870</v>
+        <v>132621888</v>
       </c>
       <c r="B149" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16338,21 +16338,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410249</v>
+        <v>410330</v>
       </c>
       <c r="R149" t="n">
-        <v>6741544</v>
+        <v>6741585</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132621865</v>
+        <v>132621906</v>
       </c>
       <c r="B150" t="n">
-        <v>79952</v>
+        <v>81318</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16435,21 +16435,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410608</v>
+        <v>410318</v>
       </c>
       <c r="R150" t="n">
-        <v>6741559</v>
+        <v>6741598</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -14678,10 +14678,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132621934</v>
+        <v>132621866</v>
       </c>
       <c r="B132" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14689,21 +14689,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>410703</v>
+        <v>410320</v>
       </c>
       <c r="R132" t="n">
-        <v>6741600</v>
+        <v>6741612</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132621866</v>
+        <v>132621934</v>
       </c>
       <c r="B133" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>410320</v>
+        <v>410703</v>
       </c>
       <c r="R133" t="n">
-        <v>6741612</v>
+        <v>6741600</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15357,10 +15357,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132621921</v>
+        <v>132621909</v>
       </c>
       <c r="B139" t="n">
-        <v>91932</v>
+        <v>81318</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15368,21 +15368,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>410323</v>
+        <v>410246</v>
       </c>
       <c r="R139" t="n">
-        <v>6741552</v>
+        <v>6741556</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15454,7 +15454,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132621909</v>
+        <v>132621910</v>
       </c>
       <c r="B140" t="n">
         <v>81318</v>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>410246</v>
+        <v>410252</v>
       </c>
       <c r="R140" t="n">
-        <v>6741556</v>
+        <v>6741547</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132621910</v>
+        <v>132621858</v>
       </c>
       <c r="B141" t="n">
-        <v>81318</v>
+        <v>79365</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410252</v>
+        <v>410236</v>
       </c>
       <c r="R141" t="n">
-        <v>6741547</v>
+        <v>6741532</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15641,17 +15641,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132621858</v>
+        <v>132621921</v>
       </c>
       <c r="B142" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15659,21 +15659,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>410236</v>
+        <v>410323</v>
       </c>
       <c r="R142" t="n">
-        <v>6741532</v>
+        <v>6741552</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132621870</v>
+        <v>132621906</v>
       </c>
       <c r="B147" t="n">
-        <v>79952</v>
+        <v>81318</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410249</v>
+        <v>410318</v>
       </c>
       <c r="R147" t="n">
-        <v>6741544</v>
+        <v>6741598</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132621865</v>
+        <v>132621888</v>
       </c>
       <c r="B148" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16241,21 +16241,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410608</v>
+        <v>410330</v>
       </c>
       <c r="R148" t="n">
-        <v>6741559</v>
+        <v>6741585</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16320,17 +16320,17 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132621888</v>
+        <v>132621870</v>
       </c>
       <c r="B149" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16338,21 +16338,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410330</v>
+        <v>410249</v>
       </c>
       <c r="R149" t="n">
-        <v>6741585</v>
+        <v>6741544</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132621906</v>
+        <v>132621865</v>
       </c>
       <c r="B150" t="n">
-        <v>81318</v>
+        <v>79952</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16435,21 +16435,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410318</v>
+        <v>410608</v>
       </c>
       <c r="R150" t="n">
-        <v>6741598</v>
+        <v>6741559</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16812,10 +16812,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132621885</v>
+        <v>132621943</v>
       </c>
       <c r="B154" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16823,21 +16823,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16847,10 +16847,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>410220</v>
+        <v>410209</v>
       </c>
       <c r="R154" t="n">
-        <v>6741586</v>
+        <v>6741614</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16909,10 +16909,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132621943</v>
+        <v>132621885</v>
       </c>
       <c r="B155" t="n">
-        <v>78999</v>
+        <v>79923</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>410209</v>
+        <v>410220</v>
       </c>
       <c r="R155" t="n">
-        <v>6741614</v>
+        <v>6741586</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -15260,10 +15260,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132621900</v>
+        <v>132621858</v>
       </c>
       <c r="B138" t="n">
-        <v>79091</v>
+        <v>79365</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15271,21 +15271,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>410323</v>
+        <v>410236</v>
       </c>
       <c r="R138" t="n">
-        <v>6741612</v>
+        <v>6741532</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132621858</v>
+        <v>132621921</v>
       </c>
       <c r="B141" t="n">
-        <v>79365</v>
+        <v>91932</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410236</v>
+        <v>410323</v>
       </c>
       <c r="R141" t="n">
-        <v>6741532</v>
+        <v>6741552</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15641,17 +15641,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132621921</v>
+        <v>132621900</v>
       </c>
       <c r="B142" t="n">
-        <v>91932</v>
+        <v>79091</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15659,21 +15659,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
         <v>410323</v>
       </c>
       <c r="R142" t="n">
-        <v>6741552</v>
+        <v>6741612</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132621906</v>
+        <v>132621870</v>
       </c>
       <c r="B147" t="n">
-        <v>81318</v>
+        <v>79952</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410318</v>
+        <v>410249</v>
       </c>
       <c r="R147" t="n">
-        <v>6741598</v>
+        <v>6741544</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132621888</v>
+        <v>132621865</v>
       </c>
       <c r="B148" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16241,21 +16241,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410330</v>
+        <v>410608</v>
       </c>
       <c r="R148" t="n">
-        <v>6741585</v>
+        <v>6741559</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16320,17 +16320,17 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132621870</v>
+        <v>132621906</v>
       </c>
       <c r="B149" t="n">
-        <v>79952</v>
+        <v>81318</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16338,21 +16338,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410249</v>
+        <v>410318</v>
       </c>
       <c r="R149" t="n">
-        <v>6741544</v>
+        <v>6741598</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132621865</v>
+        <v>132621888</v>
       </c>
       <c r="B150" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16435,21 +16435,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410608</v>
+        <v>410330</v>
       </c>
       <c r="R150" t="n">
-        <v>6741559</v>
+        <v>6741585</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16812,10 +16812,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132621943</v>
+        <v>132621885</v>
       </c>
       <c r="B154" t="n">
-        <v>78999</v>
+        <v>79923</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16823,21 +16823,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16847,10 +16847,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>410209</v>
+        <v>410220</v>
       </c>
       <c r="R154" t="n">
-        <v>6741614</v>
+        <v>6741586</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16909,10 +16909,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132621885</v>
+        <v>132621943</v>
       </c>
       <c r="B155" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>410220</v>
+        <v>410209</v>
       </c>
       <c r="R155" t="n">
-        <v>6741586</v>
+        <v>6741614</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -15260,10 +15260,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132621858</v>
+        <v>132621909</v>
       </c>
       <c r="B138" t="n">
-        <v>79365</v>
+        <v>81318</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15271,21 +15271,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>410236</v>
+        <v>410246</v>
       </c>
       <c r="R138" t="n">
-        <v>6741532</v>
+        <v>6741556</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15350,14 +15350,14 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132621909</v>
+        <v>132621910</v>
       </c>
       <c r="B139" t="n">
         <v>81318</v>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>410246</v>
+        <v>410252</v>
       </c>
       <c r="R139" t="n">
-        <v>6741556</v>
+        <v>6741547</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15454,10 +15454,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132621910</v>
+        <v>132621921</v>
       </c>
       <c r="B140" t="n">
-        <v>81318</v>
+        <v>91932</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15465,21 +15465,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>410252</v>
+        <v>410323</v>
       </c>
       <c r="R140" t="n">
-        <v>6741547</v>
+        <v>6741552</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132621921</v>
+        <v>132621858</v>
       </c>
       <c r="B141" t="n">
-        <v>91932</v>
+        <v>79365</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410323</v>
+        <v>410236</v>
       </c>
       <c r="R141" t="n">
-        <v>6741552</v>
+        <v>6741532</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132621870</v>
+        <v>132621906</v>
       </c>
       <c r="B147" t="n">
-        <v>79952</v>
+        <v>81318</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410249</v>
+        <v>410318</v>
       </c>
       <c r="R147" t="n">
-        <v>6741544</v>
+        <v>6741598</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132621865</v>
+        <v>132621888</v>
       </c>
       <c r="B148" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16241,21 +16241,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410608</v>
+        <v>410330</v>
       </c>
       <c r="R148" t="n">
-        <v>6741559</v>
+        <v>6741585</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16320,17 +16320,17 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132621906</v>
+        <v>132621865</v>
       </c>
       <c r="B149" t="n">
-        <v>81318</v>
+        <v>79952</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16338,21 +16338,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410318</v>
+        <v>410608</v>
       </c>
       <c r="R149" t="n">
-        <v>6741598</v>
+        <v>6741559</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16417,17 +16417,17 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132621888</v>
+        <v>132621870</v>
       </c>
       <c r="B150" t="n">
-        <v>91918</v>
+        <v>79952</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16435,21 +16435,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410330</v>
+        <v>410249</v>
       </c>
       <c r="R150" t="n">
-        <v>6741585</v>
+        <v>6741544</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16812,10 +16812,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132621885</v>
+        <v>132621943</v>
       </c>
       <c r="B154" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16823,21 +16823,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16847,10 +16847,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>410220</v>
+        <v>410209</v>
       </c>
       <c r="R154" t="n">
-        <v>6741586</v>
+        <v>6741614</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16909,10 +16909,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132621943</v>
+        <v>132621885</v>
       </c>
       <c r="B155" t="n">
-        <v>78999</v>
+        <v>79923</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16920,21 +16920,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16944,10 +16944,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>410209</v>
+        <v>410220</v>
       </c>
       <c r="R155" t="n">
-        <v>6741614</v>
+        <v>6741586</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb, Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb, Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY197"/>
+  <dimension ref="A1:AY200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12219,7 +12219,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131809075</v>
+        <v>131809063</v>
       </c>
       <c r="B113" t="n">
         <v>79373</v>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>410589</v>
+        <v>410431</v>
       </c>
       <c r="R113" t="n">
-        <v>6741618</v>
+        <v>6741586</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12292,12 +12292,18 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12316,7 +12322,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132621929</v>
+        <v>131809064</v>
       </c>
       <c r="B114" t="n">
         <v>79373</v>
@@ -12351,13 +12357,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>410252</v>
+        <v>410544</v>
       </c>
       <c r="R114" t="n">
-        <v>6741580</v>
+        <v>6741621</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12381,12 +12387,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12395,6 +12406,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12406,14 +12418,14 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132621930</v>
+        <v>131809075</v>
       </c>
       <c r="B115" t="n">
         <v>79373</v>
@@ -12448,13 +12460,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>410227</v>
+        <v>410589</v>
       </c>
       <c r="R115" t="n">
-        <v>6741630</v>
+        <v>6741618</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12478,12 +12490,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12503,14 +12515,14 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132621934</v>
+        <v>132621927</v>
       </c>
       <c r="B116" t="n">
         <v>79373</v>
@@ -12545,10 +12557,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>410703</v>
+        <v>410389</v>
       </c>
       <c r="R116" t="n">
-        <v>6741600</v>
+        <v>6741517</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12583,12 +12595,18 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12607,7 +12625,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132621937</v>
+        <v>132621929</v>
       </c>
       <c r="B117" t="n">
         <v>79373</v>
@@ -12642,10 +12660,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>410210</v>
+        <v>410252</v>
       </c>
       <c r="R117" t="n">
-        <v>6741587</v>
+        <v>6741580</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12704,32 +12722,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806457</v>
+        <v>132621930</v>
       </c>
       <c r="B118" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12739,13 +12757,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>410123</v>
+        <v>410227</v>
       </c>
       <c r="R118" t="n">
-        <v>6741557</v>
+        <v>6741630</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12769,22 +12787,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12799,44 +12807,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131809042</v>
+        <v>132621934</v>
       </c>
       <c r="B119" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12846,13 +12854,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>410318</v>
+        <v>410703</v>
       </c>
       <c r="R119" t="n">
-        <v>6741647</v>
+        <v>6741600</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12876,12 +12884,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12890,7 +12898,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12902,39 +12909,39 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806354</v>
+        <v>132621937</v>
       </c>
       <c r="B120" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12944,13 +12951,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>410598</v>
+        <v>410210</v>
       </c>
       <c r="R120" t="n">
-        <v>6741624</v>
+        <v>6741587</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12974,22 +12981,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13004,44 +13001,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806489</v>
+        <v>131806457</v>
       </c>
       <c r="B121" t="n">
-        <v>78776</v>
+        <v>79397</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13051,10 +13048,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>410191</v>
+        <v>410123</v>
       </c>
       <c r="R121" t="n">
-        <v>6741549</v>
+        <v>6741557</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13086,7 +13083,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13096,12 +13093,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På torraka med fyra brnadljud</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13128,48 +13120,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131808974</v>
+        <v>131809042</v>
       </c>
       <c r="B122" t="n">
-        <v>83358</v>
+        <v>79397</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>410339</v>
+        <v>410318</v>
       </c>
       <c r="R122" t="n">
-        <v>6741540</v>
+        <v>6741647</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13222,17 +13211,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131808975</v>
+        <v>131806354</v>
       </c>
       <c r="B123" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13240,40 +13229,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>410579</v>
+        <v>410598</v>
       </c>
       <c r="R123" t="n">
-        <v>6741619</v>
+        <v>6741624</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13300,40 +13286,49 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131808976</v>
+        <v>131806489</v>
       </c>
       <c r="B124" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13341,40 +13336,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>410372</v>
+        <v>410191</v>
       </c>
       <c r="R124" t="n">
-        <v>6741606</v>
+        <v>6741549</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13401,37 +13393,51 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På torraka med fyra brnadljud</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131808978</v>
+        <v>131808974</v>
       </c>
       <c r="B125" t="n">
         <v>83358</v>
@@ -13469,10 +13475,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>410571</v>
+        <v>410339</v>
       </c>
       <c r="R125" t="n">
-        <v>6741621</v>
+        <v>6741540</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13532,7 +13538,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131808980</v>
+        <v>131808975</v>
       </c>
       <c r="B126" t="n">
         <v>83358</v>
@@ -13570,10 +13576,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>410551</v>
+        <v>410579</v>
       </c>
       <c r="R126" t="n">
-        <v>6741611</v>
+        <v>6741619</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13633,7 +13639,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131808983</v>
+        <v>131808976</v>
       </c>
       <c r="B127" t="n">
         <v>83358</v>
@@ -13671,10 +13677,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>410580</v>
+        <v>410372</v>
       </c>
       <c r="R127" t="n">
-        <v>6741625</v>
+        <v>6741606</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13734,32 +13740,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132621915</v>
+        <v>131808978</v>
       </c>
       <c r="B128" t="n">
-        <v>78731</v>
+        <v>83358</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13772,13 +13778,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>410346</v>
+        <v>410571</v>
       </c>
       <c r="R128" t="n">
-        <v>6741646</v>
+        <v>6741621</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13802,12 +13808,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13828,17 +13834,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131806458</v>
+        <v>131808980</v>
       </c>
       <c r="B129" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13846,37 +13852,40 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>410123</v>
+        <v>410551</v>
       </c>
       <c r="R129" t="n">
-        <v>6741558</v>
+        <v>6741611</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13903,49 +13912,40 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131806456</v>
+        <v>131808983</v>
       </c>
       <c r="B130" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13953,37 +13953,40 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>410123</v>
+        <v>410580</v>
       </c>
       <c r="R130" t="n">
-        <v>6741558</v>
+        <v>6741625</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14010,87 +14013,81 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131809008</v>
+        <v>132621915</v>
       </c>
       <c r="B131" t="n">
-        <v>79992</v>
+        <v>78731</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6443</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>410253</v>
+        <v>410346</v>
       </c>
       <c r="R131" t="n">
-        <v>6741548</v>
+        <v>6741646</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14114,12 +14111,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14128,6 +14125,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14139,17 +14137,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132621865</v>
+        <v>131806458</v>
       </c>
       <c r="B132" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14157,21 +14155,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14181,13 +14179,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>410608</v>
+        <v>410123</v>
       </c>
       <c r="R132" t="n">
-        <v>6741559</v>
+        <v>6741558</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14211,12 +14209,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,19 +14239,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132621866</v>
+        <v>131806456</v>
       </c>
       <c r="B133" t="n">
         <v>79992</v>
@@ -14278,13 +14286,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>410320</v>
+        <v>410123</v>
       </c>
       <c r="R133" t="n">
-        <v>6741612</v>
+        <v>6741558</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14308,12 +14316,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14328,19 +14346,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132621870</v>
+        <v>131809008</v>
       </c>
       <c r="B134" t="n">
         <v>79992</v>
@@ -14375,13 +14393,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>410249</v>
+        <v>410253</v>
       </c>
       <c r="R134" t="n">
-        <v>6741544</v>
+        <v>6741548</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14405,12 +14423,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14430,14 +14448,14 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132621871</v>
+        <v>132621865</v>
       </c>
       <c r="B135" t="n">
         <v>79992</v>
@@ -14472,10 +14490,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>410252</v>
+        <v>410608</v>
       </c>
       <c r="R135" t="n">
-        <v>6741545</v>
+        <v>6741559</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14527,14 +14545,14 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132621872</v>
+        <v>132621866</v>
       </c>
       <c r="B136" t="n">
         <v>79992</v>
@@ -14569,7 +14587,7 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>410206</v>
+        <v>410320</v>
       </c>
       <c r="R136" t="n">
         <v>6741612</v>
@@ -14631,7 +14649,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132621875</v>
+        <v>132621870</v>
       </c>
       <c r="B137" t="n">
         <v>79992</v>
@@ -14666,10 +14684,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>410349</v>
+        <v>410249</v>
       </c>
       <c r="R137" t="n">
-        <v>6741643</v>
+        <v>6741544</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14728,7 +14746,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132621877</v>
+        <v>132621871</v>
       </c>
       <c r="B138" t="n">
         <v>79992</v>
@@ -14763,10 +14781,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>410687</v>
+        <v>410252</v>
       </c>
       <c r="R138" t="n">
-        <v>6741620</v>
+        <v>6741545</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14825,10 +14843,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131806522</v>
+        <v>132621872</v>
       </c>
       <c r="B139" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14836,21 +14854,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14860,13 +14878,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>410192</v>
+        <v>410206</v>
       </c>
       <c r="R139" t="n">
-        <v>6741630</v>
+        <v>6741612</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14890,22 +14908,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14920,22 +14928,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131812551</v>
+        <v>132621875</v>
       </c>
       <c r="B140" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14943,40 +14951,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>410589</v>
+        <v>410349</v>
       </c>
       <c r="R140" t="n">
-        <v>6741618</v>
+        <v>6741643</v>
       </c>
       <c r="S140" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15000,12 +15005,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15014,7 +15019,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15026,60 +15030,55 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131806416</v>
+        <v>132621877</v>
       </c>
       <c r="B141" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410352</v>
+        <v>410687</v>
       </c>
       <c r="R141" t="n">
-        <v>6741580</v>
+        <v>6741620</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15103,27 +15102,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>I torraka</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15138,62 +15122,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131806435</v>
+        <v>131806522</v>
       </c>
       <c r="B142" t="n">
-        <v>57972</v>
+        <v>78377</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>410257</v>
+        <v>410192</v>
       </c>
       <c r="R142" t="n">
-        <v>6741554</v>
+        <v>6741630</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15225,7 +15204,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15235,7 +15214,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15262,53 +15241,51 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131806473</v>
+        <v>131812551</v>
       </c>
       <c r="B143" t="n">
-        <v>57972</v>
+        <v>78377</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>410166</v>
+        <v>410589</v>
       </c>
       <c r="R143" t="n">
-        <v>6741550</v>
+        <v>6741618</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15335,66 +15312,57 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131806351</v>
+        <v>131806416</v>
       </c>
       <c r="B144" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15405,7 +15373,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15414,10 +15382,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>410470</v>
+        <v>410352</v>
       </c>
       <c r="R144" t="n">
-        <v>6741635</v>
+        <v>6741580</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15449,7 +15417,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15459,7 +15427,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>I torraka</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15486,27 +15459,27 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131806364</v>
+        <v>131806435</v>
       </c>
       <c r="B145" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15517,7 +15490,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15526,10 +15499,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>410774</v>
+        <v>410257</v>
       </c>
       <c r="R145" t="n">
-        <v>6741570</v>
+        <v>6741554</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15561,7 +15534,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15571,12 +15544,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Skalad smågran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15603,27 +15571,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131806369</v>
+        <v>131806473</v>
       </c>
       <c r="B146" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15634,7 +15602,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15643,10 +15611,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>410731</v>
+        <v>410166</v>
       </c>
       <c r="R146" t="n">
-        <v>6741576</v>
+        <v>6741550</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15678,7 +15646,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15688,7 +15656,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15715,7 +15683,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131806373</v>
+        <v>131806351</v>
       </c>
       <c r="B147" t="n">
         <v>57975</v>
@@ -15755,10 +15723,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410655</v>
+        <v>410470</v>
       </c>
       <c r="R147" t="n">
-        <v>6741583</v>
+        <v>6741635</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15790,7 +15758,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15800,7 +15768,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15827,7 +15795,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131806384</v>
+        <v>131806364</v>
       </c>
       <c r="B148" t="n">
         <v>57975</v>
@@ -15867,10 +15835,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410549</v>
+        <v>410774</v>
       </c>
       <c r="R148" t="n">
-        <v>6741560</v>
+        <v>6741570</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15902,7 +15870,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15912,7 +15880,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Skalad smågran</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15939,7 +15912,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131806385</v>
+        <v>131806369</v>
       </c>
       <c r="B149" t="n">
         <v>57975</v>
@@ -15979,10 +15952,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410544</v>
+        <v>410731</v>
       </c>
       <c r="R149" t="n">
-        <v>6741545</v>
+        <v>6741576</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16014,7 +15987,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16024,7 +15997,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16051,7 +16024,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131806391</v>
+        <v>131806373</v>
       </c>
       <c r="B150" t="n">
         <v>57975</v>
@@ -16091,10 +16064,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410512</v>
+        <v>410655</v>
       </c>
       <c r="R150" t="n">
-        <v>6741584</v>
+        <v>6741583</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16126,7 +16099,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16136,7 +16109,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16163,7 +16136,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131806395</v>
+        <v>131806384</v>
       </c>
       <c r="B151" t="n">
         <v>57975</v>
@@ -16203,10 +16176,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>410502</v>
+        <v>410549</v>
       </c>
       <c r="R151" t="n">
-        <v>6741573</v>
+        <v>6741560</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16238,7 +16211,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16248,7 +16221,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16275,7 +16248,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131806396</v>
+        <v>131806385</v>
       </c>
       <c r="B152" t="n">
         <v>57975</v>
@@ -16306,7 +16279,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -16315,10 +16288,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>410485</v>
+        <v>410544</v>
       </c>
       <c r="R152" t="n">
-        <v>6741564</v>
+        <v>6741545</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16350,7 +16323,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16360,12 +16333,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16392,7 +16360,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131806397</v>
+        <v>131806391</v>
       </c>
       <c r="B153" t="n">
         <v>57975</v>
@@ -16432,10 +16400,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>410490</v>
+        <v>410512</v>
       </c>
       <c r="R153" t="n">
-        <v>6741572</v>
+        <v>6741584</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16467,7 +16435,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16477,7 +16445,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16504,7 +16472,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131806399</v>
+        <v>131806395</v>
       </c>
       <c r="B154" t="n">
         <v>57975</v>
@@ -16544,10 +16512,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>410482</v>
+        <v>410502</v>
       </c>
       <c r="R154" t="n">
-        <v>6741564</v>
+        <v>6741573</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16579,7 +16547,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16589,12 +16557,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16621,7 +16584,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131806407</v>
+        <v>131806396</v>
       </c>
       <c r="B155" t="n">
         <v>57975</v>
@@ -16652,7 +16615,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -16661,10 +16624,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>410432</v>
+        <v>410485</v>
       </c>
       <c r="R155" t="n">
-        <v>6741569</v>
+        <v>6741564</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16696,7 +16659,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16706,12 +16669,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Skalad smågran</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16738,7 +16701,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131806408</v>
+        <v>131806397</v>
       </c>
       <c r="B156" t="n">
         <v>57975</v>
@@ -16769,7 +16732,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -16778,10 +16741,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>410427</v>
+        <v>410490</v>
       </c>
       <c r="R156" t="n">
-        <v>6741574</v>
+        <v>6741572</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16813,7 +16776,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16823,12 +16786,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16855,7 +16813,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131806434</v>
+        <v>131806399</v>
       </c>
       <c r="B157" t="n">
         <v>57975</v>
@@ -16886,7 +16844,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -16895,10 +16853,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>410257</v>
+        <v>410482</v>
       </c>
       <c r="R157" t="n">
-        <v>6741554</v>
+        <v>6741564</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16930,7 +16888,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16940,7 +16898,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16967,7 +16930,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131806440</v>
+        <v>131806407</v>
       </c>
       <c r="B158" t="n">
         <v>57975</v>
@@ -16998,7 +16961,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -17007,10 +16970,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>410216</v>
+        <v>410432</v>
       </c>
       <c r="R158" t="n">
-        <v>6741551</v>
+        <v>6741569</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17042,7 +17005,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17052,7 +17015,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Skalad smågran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17079,7 +17047,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131806449</v>
+        <v>131806408</v>
       </c>
       <c r="B159" t="n">
         <v>57975</v>
@@ -17119,10 +17087,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>410117</v>
+        <v>410427</v>
       </c>
       <c r="R159" t="n">
-        <v>6741596</v>
+        <v>6741574</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17154,7 +17122,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17164,12 +17132,12 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17196,7 +17164,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131806478</v>
+        <v>131806434</v>
       </c>
       <c r="B160" t="n">
         <v>57975</v>
@@ -17227,7 +17195,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17236,10 +17204,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>410174</v>
+        <v>410257</v>
       </c>
       <c r="R160" t="n">
-        <v>6741529</v>
+        <v>6741554</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17271,7 +17239,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17281,7 +17249,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17308,7 +17276,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131806482</v>
+        <v>131806440</v>
       </c>
       <c r="B161" t="n">
         <v>57975</v>
@@ -17339,7 +17307,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -17348,10 +17316,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>410178</v>
+        <v>410216</v>
       </c>
       <c r="R161" t="n">
-        <v>6741516</v>
+        <v>6741551</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17383,7 +17351,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17393,7 +17361,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17420,7 +17388,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131806491</v>
+        <v>131806449</v>
       </c>
       <c r="B162" t="n">
         <v>57975</v>
@@ -17451,7 +17419,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -17460,10 +17428,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>410195</v>
+        <v>410117</v>
       </c>
       <c r="R162" t="n">
-        <v>6741554</v>
+        <v>6741596</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17495,7 +17463,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17505,7 +17473,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17532,7 +17505,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131806494</v>
+        <v>131806478</v>
       </c>
       <c r="B163" t="n">
         <v>57975</v>
@@ -17572,10 +17545,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>410192</v>
+        <v>410174</v>
       </c>
       <c r="R163" t="n">
-        <v>6741561</v>
+        <v>6741529</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17607,7 +17580,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17617,7 +17590,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17644,7 +17617,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131806497</v>
+        <v>131806482</v>
       </c>
       <c r="B164" t="n">
         <v>57975</v>
@@ -17684,10 +17657,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>410197</v>
+        <v>410178</v>
       </c>
       <c r="R164" t="n">
-        <v>6741577</v>
+        <v>6741516</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17719,7 +17692,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17729,7 +17702,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17756,7 +17729,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131806507</v>
+        <v>131806491</v>
       </c>
       <c r="B165" t="n">
         <v>57975</v>
@@ -17796,10 +17769,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>410221</v>
+        <v>410195</v>
       </c>
       <c r="R165" t="n">
-        <v>6741596</v>
+        <v>6741554</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17831,7 +17804,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17841,7 +17814,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17868,7 +17841,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>131809020</v>
+        <v>131806494</v>
       </c>
       <c r="B166" t="n">
         <v>57975</v>
@@ -17897,19 +17870,24 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>410369</v>
+        <v>410192</v>
       </c>
       <c r="R166" t="n">
-        <v>6741611</v>
+        <v>6741561</v>
       </c>
       <c r="S166" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17936,9 +17914,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17953,19 +17941,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131809023</v>
+        <v>131806497</v>
       </c>
       <c r="B167" t="n">
         <v>57975</v>
@@ -17994,19 +17982,24 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>410476</v>
+        <v>410197</v>
       </c>
       <c r="R167" t="n">
-        <v>6741605</v>
+        <v>6741577</v>
       </c>
       <c r="S167" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18033,9 +18026,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18050,19 +18053,19 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131809026</v>
+        <v>131806507</v>
       </c>
       <c r="B168" t="n">
         <v>57975</v>
@@ -18091,27 +18094,24 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>410354</v>
+        <v>410221</v>
       </c>
       <c r="R168" t="n">
-        <v>6741532</v>
+        <v>6741596</v>
       </c>
       <c r="S168" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18138,14 +18138,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18160,19 +18165,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131809027</v>
+        <v>131809020</v>
       </c>
       <c r="B169" t="n">
         <v>57975</v>
@@ -18201,24 +18206,16 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>410356</v>
+        <v>410369</v>
       </c>
       <c r="R169" t="n">
-        <v>6741540</v>
+        <v>6741611</v>
       </c>
       <c r="S169" t="n">
         <v>20</v>
@@ -18251,11 +18248,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18282,7 +18274,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131809028</v>
+        <v>131809023</v>
       </c>
       <c r="B170" t="n">
         <v>57975</v>
@@ -18311,24 +18303,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>410423</v>
+        <v>410476</v>
       </c>
       <c r="R170" t="n">
-        <v>6741606</v>
+        <v>6741605</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -18361,11 +18345,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18392,7 +18371,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131809031</v>
+        <v>131809026</v>
       </c>
       <c r="B171" t="n">
         <v>57975</v>
@@ -18435,10 +18414,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>410355</v>
+        <v>410354</v>
       </c>
       <c r="R171" t="n">
-        <v>6741540</v>
+        <v>6741532</v>
       </c>
       <c r="S171" t="n">
         <v>20</v>
@@ -18502,7 +18481,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131809034</v>
+        <v>131809027</v>
       </c>
       <c r="B172" t="n">
         <v>57975</v>
@@ -18545,10 +18524,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>410416</v>
+        <v>410356</v>
       </c>
       <c r="R172" t="n">
-        <v>6741600</v>
+        <v>6741540</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -18612,7 +18591,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131809035</v>
+        <v>131809028</v>
       </c>
       <c r="B173" t="n">
         <v>57975</v>
@@ -18655,10 +18634,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>410502</v>
+        <v>410423</v>
       </c>
       <c r="R173" t="n">
-        <v>6741621</v>
+        <v>6741606</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -18722,53 +18701,56 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131806363</v>
+        <v>131809031</v>
       </c>
       <c r="B174" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>410766</v>
+        <v>410355</v>
       </c>
       <c r="R174" t="n">
-        <v>6741592</v>
+        <v>6741540</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18795,19 +18777,14 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>12:26</t>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18822,65 +18799,68 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131806499</v>
+        <v>131809034</v>
       </c>
       <c r="B175" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>410179</v>
+        <v>410416</v>
       </c>
       <c r="R175" t="n">
-        <v>6741569</v>
+        <v>6741600</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18907,19 +18887,14 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18934,65 +18909,68 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131806514</v>
+        <v>131809035</v>
       </c>
       <c r="B176" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>410257</v>
+        <v>410502</v>
       </c>
       <c r="R176" t="n">
-        <v>6741601</v>
+        <v>6741621</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19019,19 +18997,14 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>10:36</t>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19046,19 +19019,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>132621893</v>
+        <v>131806363</v>
       </c>
       <c r="B177" t="n">
         <v>57162</v>
@@ -19086,9 +19059,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19097,13 +19071,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>410712</v>
+        <v>410766</v>
       </c>
       <c r="R177" t="n">
-        <v>6741559</v>
+        <v>6741592</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19127,12 +19101,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19147,22 +19131,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131806498</v>
+        <v>131806499</v>
       </c>
       <c r="B178" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19170,27 +19154,27 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19199,10 +19183,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>410197</v>
+        <v>410179</v>
       </c>
       <c r="R178" t="n">
-        <v>6741577</v>
+        <v>6741569</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19234,7 +19218,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19244,7 +19228,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19271,38 +19255,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131806358</v>
+        <v>131806514</v>
       </c>
       <c r="B179" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19311,10 +19295,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>410709</v>
+        <v>410257</v>
       </c>
       <c r="R179" t="n">
-        <v>6741602</v>
+        <v>6741601</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19346,7 +19330,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19356,7 +19340,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19383,32 +19367,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131806441</v>
+        <v>132621893</v>
       </c>
       <c r="B180" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -19422,13 +19406,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>410179</v>
+        <v>410712</v>
       </c>
       <c r="R180" t="n">
-        <v>6741551</v>
+        <v>6741559</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19452,22 +19436,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19482,22 +19456,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131806429</v>
+        <v>131806498</v>
       </c>
       <c r="B181" t="n">
-        <v>8460</v>
+        <v>5181</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19505,21 +19479,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19534,10 +19508,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>410279</v>
+        <v>410197</v>
       </c>
       <c r="R181" t="n">
-        <v>6741504</v>
+        <v>6741577</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19569,7 +19543,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19579,7 +19553,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19606,38 +19580,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131806444</v>
+        <v>131806358</v>
       </c>
       <c r="B182" t="n">
-        <v>8460</v>
+        <v>58136</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -19646,10 +19620,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>410225</v>
+        <v>410709</v>
       </c>
       <c r="R182" t="n">
-        <v>6741556</v>
+        <v>6741602</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19681,7 +19655,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19691,7 +19665,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19718,38 +19692,37 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131806450</v>
+        <v>131806441</v>
       </c>
       <c r="B183" t="n">
-        <v>8460</v>
+        <v>58136</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -19758,10 +19731,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>410130</v>
+        <v>410179</v>
       </c>
       <c r="R183" t="n">
-        <v>6741614</v>
+        <v>6741551</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19793,7 +19766,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19803,7 +19776,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19830,7 +19803,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>131806493</v>
+        <v>131806429</v>
       </c>
       <c r="B184" t="n">
         <v>8460</v>
@@ -19870,10 +19843,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>410203</v>
+        <v>410279</v>
       </c>
       <c r="R184" t="n">
-        <v>6741568</v>
+        <v>6741504</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19905,7 +19878,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19915,7 +19888,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19942,7 +19915,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>131806519</v>
+        <v>131806444</v>
       </c>
       <c r="B185" t="n">
         <v>8460</v>
@@ -19982,10 +19955,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>410240</v>
+        <v>410225</v>
       </c>
       <c r="R185" t="n">
-        <v>6741632</v>
+        <v>6741556</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20017,7 +19990,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20027,7 +20000,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20054,10 +20027,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>131806370</v>
+        <v>131806450</v>
       </c>
       <c r="B186" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20065,21 +20038,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20094,10 +20067,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>410677</v>
+        <v>410130</v>
       </c>
       <c r="R186" t="n">
-        <v>6741573</v>
+        <v>6741614</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20129,7 +20102,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20139,7 +20112,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20166,48 +20139,53 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>132611050</v>
+        <v>131806493</v>
       </c>
       <c r="B187" t="n">
-        <v>56706</v>
+        <v>8460</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>410504</v>
+        <v>410203</v>
       </c>
       <c r="R187" t="n">
-        <v>6741536</v>
+        <v>6741568</v>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20231,12 +20209,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20251,60 +20239,65 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>132611057</v>
+        <v>131806519</v>
       </c>
       <c r="B188" t="n">
-        <v>79131</v>
+        <v>8460</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>410329</v>
+        <v>410240</v>
       </c>
       <c r="R188" t="n">
-        <v>6741593</v>
+        <v>6741632</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20328,12 +20321,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20348,60 +20351,65 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>132611058</v>
+        <v>131806370</v>
       </c>
       <c r="B189" t="n">
-        <v>79131</v>
+        <v>8449</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>410279</v>
+        <v>410677</v>
       </c>
       <c r="R189" t="n">
-        <v>6741644</v>
+        <v>6741573</v>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20425,12 +20433,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20445,22 +20463,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>132621900</v>
+        <v>132611050</v>
       </c>
       <c r="B190" t="n">
-        <v>79131</v>
+        <v>56706</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20468,21 +20486,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>228912</v>
+        <v>206046</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20492,13 +20510,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>410323</v>
+        <v>410504</v>
       </c>
       <c r="R190" t="n">
-        <v>6741612</v>
+        <v>6741536</v>
       </c>
       <c r="S190" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20542,22 +20560,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>70327925</v>
+        <v>132611057</v>
       </c>
       <c r="B191" t="n">
-        <v>79917</v>
+        <v>79131</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20565,21 +20583,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20589,13 +20607,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>410671</v>
+        <v>410329</v>
       </c>
       <c r="R191" t="n">
-        <v>6741622</v>
+        <v>6741593</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20619,12 +20637,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20639,22 +20657,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>131806346</v>
+        <v>132611058</v>
       </c>
       <c r="B192" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20662,21 +20680,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20686,13 +20704,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>410348</v>
+        <v>410279</v>
       </c>
       <c r="R192" t="n">
-        <v>6741643</v>
+        <v>6741644</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20716,22 +20734,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20746,22 +20754,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>131806376</v>
+        <v>132621900</v>
       </c>
       <c r="B193" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20769,21 +20777,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20793,13 +20801,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>410612</v>
+        <v>410323</v>
       </c>
       <c r="R193" t="n">
-        <v>6741582</v>
+        <v>6741612</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20823,22 +20831,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20853,22 +20851,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>131806463</v>
+        <v>70327925</v>
       </c>
       <c r="B194" t="n">
-        <v>79963</v>
+        <v>79917</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20900,10 +20898,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>410119</v>
+        <v>410671</v>
       </c>
       <c r="R194" t="n">
-        <v>6741530</v>
+        <v>6741622</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20930,22 +20928,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20960,19 +20948,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>131806466</v>
+        <v>131806346</v>
       </c>
       <c r="B195" t="n">
         <v>79963</v>
@@ -21007,10 +20995,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>410128</v>
+        <v>410348</v>
       </c>
       <c r="R195" t="n">
-        <v>6741527</v>
+        <v>6741643</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21042,7 +21030,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21052,7 +21040,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21079,7 +21067,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>132621878</v>
+        <v>131806376</v>
       </c>
       <c r="B196" t="n">
         <v>79963</v>
@@ -21114,13 +21102,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>410320</v>
+        <v>410612</v>
       </c>
       <c r="R196" t="n">
-        <v>6741612</v>
+        <v>6741582</v>
       </c>
       <c r="S196" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21144,12 +21132,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21164,19 +21162,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>132621885</v>
+        <v>131806463</v>
       </c>
       <c r="B197" t="n">
         <v>79963</v>
@@ -21211,13 +21209,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>410220</v>
+        <v>410119</v>
       </c>
       <c r="R197" t="n">
-        <v>6741586</v>
+        <v>6741530</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21241,12 +21239,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21261,15 +21269,316 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>131806466</v>
+      </c>
+      <c r="B198" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Björnåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>410128</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6741527</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>132621878</v>
+      </c>
+      <c r="B199" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Björnåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>410320</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6741612</v>
+      </c>
+      <c r="S199" t="n">
+        <v>25</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
           <t>Moa Björnberg Dillner</t>
         </is>
       </c>
-      <c r="AX197" t="inlineStr">
+      <c r="AX199" t="inlineStr">
         <is>
           <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr"/>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>132621885</v>
+      </c>
+      <c r="B200" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Björnåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>410220</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6741586</v>
+      </c>
+      <c r="S200" t="n">
+        <v>25</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Joakim Karlsson, Ossian Tulin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Joakim Karlsson, Ossian Tulin</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY200"/>
+  <dimension ref="A1:AZ200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806479</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806367</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806417</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806422</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806495</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808988</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808989</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809003</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621857</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621858</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621859</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806437</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806445</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2417,6 +2502,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806446</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806484</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2631,6 +2726,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806492</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2743,6 +2843,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806505</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2840,6 +2945,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621943</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806413</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3044,6 +3159,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809079</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3141,6 +3261,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621947</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3238,6 +3363,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327889</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3345,6 +3475,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806377</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3452,6 +3587,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806379</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3559,6 +3699,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806462</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3666,6 +3811,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806464</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3763,6 +3913,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809054</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3860,6 +4015,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809055</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809059</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4055,6 +4220,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621905</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4152,6 +4322,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621906</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4249,6 +4424,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621907</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621909</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4443,6 +4628,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621910</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4540,6 +4730,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621911</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4637,6 +4832,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621912</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4734,6 +4934,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621913</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4831,6 +5036,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327897</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4928,6 +5138,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327936</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5035,6 +5250,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806361</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5142,6 +5362,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806398</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5249,6 +5474,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806403</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5346,6 +5576,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809011</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5443,6 +5678,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611051</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5540,6 +5780,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621887</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5637,6 +5882,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621888</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5744,6 +5994,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806390</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5841,6 +6096,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621920</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5938,6 +6198,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621921</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6045,6 +6310,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806348</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6142,6 +6412,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621922</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6239,6 +6514,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621923</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6346,6 +6626,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806350</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6453,6 +6738,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806352</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6550,6 +6840,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808984</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6647,6 +6942,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327964</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6754,6 +7054,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806518</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6861,6 +7166,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806393</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6968,6 +7278,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806401</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7075,6 +7390,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806477</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7182,6 +7502,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806347</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7289,6 +7614,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806355</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7396,6 +7726,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806356</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7503,6 +7838,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806357</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7610,6 +7950,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806359</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7717,6 +8062,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806360</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7824,6 +8174,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806366</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7931,6 +8286,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806368</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8038,6 +8398,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806372</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8145,6 +8510,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806374</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8252,6 +8622,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806381</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8359,6 +8734,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806392</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8466,6 +8846,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806394</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8573,6 +8958,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806400</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8680,6 +9070,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806406</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8787,6 +9182,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806412</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8894,6 +9294,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806415</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9001,6 +9406,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806418</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9108,6 +9518,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806424</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9215,6 +9630,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806425</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9322,6 +9742,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806431</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9429,6 +9854,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806448</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9536,6 +9966,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806451</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9643,6 +10078,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806452</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9750,6 +10190,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806453</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9857,6 +10302,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806455</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9964,6 +10414,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806459</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10071,6 +10526,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806460</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10183,6 +10643,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806468</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10290,6 +10755,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806471</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10397,6 +10867,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806474</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10504,6 +10979,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806475</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10611,6 +11091,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806476</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10718,6 +11203,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806481</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10825,6 +11315,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806483</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10932,6 +11427,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806488</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11039,6 +11539,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806496</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11146,6 +11651,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806500</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11253,6 +11763,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806502</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11360,6 +11875,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806503</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11467,6 +11987,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806504</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11574,6 +12099,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806510</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11681,6 +12211,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806511</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11788,6 +12323,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806515</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11895,6 +12435,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806517</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12002,6 +12547,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806521</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12105,6 +12655,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809063</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12208,6 +12763,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809064</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12305,6 +12865,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809075</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12408,6 +12973,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621927</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12505,6 +13075,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621929</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12602,6 +13177,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621930</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12699,6 +13279,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621934</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12796,6 +13381,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621937</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12903,6 +13493,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806457</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13001,6 +13596,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809042</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13108,6 +13708,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806354</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13220,6 +13825,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806489</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13321,6 +13931,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808974</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13422,6 +14037,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808975</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13523,6 +14143,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808976</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13624,6 +14249,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808978</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13725,6 +14355,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808980</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13826,6 +14461,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131808983</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13927,6 +14567,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621915</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14034,6 +14679,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806458</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14141,6 +14791,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806456</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14238,6 +14893,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809008</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14335,6 +14995,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621865</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14432,6 +15097,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621866</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14529,6 +15199,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621870</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14626,6 +15301,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621871</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14723,6 +15403,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621872</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14820,6 +15505,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621875</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14917,6 +15607,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621877</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15024,6 +15719,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806522</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15125,6 +15825,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131812551</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15242,6 +15947,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806416</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15354,6 +16064,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806435</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15466,6 +16181,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806473</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15578,6 +16298,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806351</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15690,6 +16415,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806369</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15802,6 +16532,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806373</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15914,6 +16649,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806384</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16026,6 +16766,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806385</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16138,6 +16883,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806391</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16250,6 +17000,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806395</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16367,6 +17122,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806396</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16479,6 +17239,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806397</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16596,6 +17361,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806399</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16713,6 +17483,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806407</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16830,6 +17605,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806408</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16942,6 +17722,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806434</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17054,6 +17839,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806440</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17171,6 +17961,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806449</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17283,6 +18078,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806478</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17395,6 +18195,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806482</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17507,6 +18312,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806491</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17619,6 +18429,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806494</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17731,6 +18546,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806497</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17843,6 +18663,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806507</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17940,6 +18765,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809020</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18037,6 +18867,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809023</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18147,6 +18982,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809026</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18257,6 +19097,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809027</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18367,6 +19212,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809028</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18477,6 +19327,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809031</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18587,6 +19442,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809034</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18697,6 +19557,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131809035</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18809,6 +19674,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806499</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18921,6 +19791,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806514</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19022,6 +19897,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621893</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19134,6 +20014,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806498</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19246,6 +20131,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806358</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19357,6 +20247,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806441</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19469,6 +20364,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806429</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19581,6 +20481,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806444</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19693,6 +20598,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806450</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19805,6 +20715,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806493</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19917,6 +20832,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806519</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20029,6 +20949,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806370</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20126,6 +21051,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611050</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20223,6 +21153,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611057</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20320,6 +21255,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132611058</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20417,6 +21357,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621900</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20514,6 +21459,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327925</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20621,6 +21571,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806346</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20728,6 +21683,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806376</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20835,6 +21795,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806463</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20942,6 +21907,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806466</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21039,6 +22009,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621878</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21136,6 +22111,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132621885</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21243,6 +22223,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806362</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21350,6 +22335,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806365</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21467,6 +22457,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806364</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21579,8 +22574,214 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806363</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ200"/>
+  <dimension ref="A1:AZ201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12771,10 +12771,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131809075</v>
+        <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79373</v>
+        <v>79444</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12806,10 +12806,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>410589</v>
+        <v>410337</v>
       </c>
       <c r="R113" t="n">
-        <v>6741618</v>
+        <v>6741538</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12844,12 +12844,18 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12867,13 +12873,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809075</t>
+          <t>https://artportalen.se/Sighting/131809073</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132621927</v>
+        <v>131809075</v>
       </c>
       <c r="B114" t="n">
         <v>79373</v>
@@ -12908,13 +12914,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>410389</v>
+        <v>410589</v>
       </c>
       <c r="R114" t="n">
-        <v>6741517</v>
+        <v>6741618</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12938,17 +12944,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Garnlavstrassel</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12957,7 +12958,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12969,19 +12969,19 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621927</t>
+          <t>https://artportalen.se/Sighting/131809075</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132621929</v>
+        <v>132621927</v>
       </c>
       <c r="B115" t="n">
         <v>79373</v>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>410252</v>
+        <v>410389</v>
       </c>
       <c r="R115" t="n">
-        <v>6741580</v>
+        <v>6741517</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13054,12 +13054,18 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13077,13 +13083,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621929</t>
+          <t>https://artportalen.se/Sighting/132621927</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132621930</v>
+        <v>132621929</v>
       </c>
       <c r="B116" t="n">
         <v>79373</v>
@@ -13118,10 +13124,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>410227</v>
+        <v>410252</v>
       </c>
       <c r="R116" t="n">
-        <v>6741630</v>
+        <v>6741580</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13179,13 +13185,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621930</t>
+          <t>https://artportalen.se/Sighting/132621929</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132621934</v>
+        <v>132621930</v>
       </c>
       <c r="B117" t="n">
         <v>79373</v>
@@ -13220,10 +13226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>410703</v>
+        <v>410227</v>
       </c>
       <c r="R117" t="n">
-        <v>6741600</v>
+        <v>6741630</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13281,13 +13287,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621934</t>
+          <t>https://artportalen.se/Sighting/132621930</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132621937</v>
+        <v>132621934</v>
       </c>
       <c r="B118" t="n">
         <v>79373</v>
@@ -13322,10 +13328,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>410210</v>
+        <v>410703</v>
       </c>
       <c r="R118" t="n">
-        <v>6741587</v>
+        <v>6741600</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13383,38 +13389,38 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621937</t>
+          <t>https://artportalen.se/Sighting/132621934</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806457</v>
+        <v>132621937</v>
       </c>
       <c r="B119" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13424,13 +13430,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>410123</v>
+        <v>410210</v>
       </c>
       <c r="R119" t="n">
-        <v>6741557</v>
+        <v>6741587</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13454,22 +13460,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13484,24 +13480,24 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806457</t>
+          <t>https://artportalen.se/Sighting/132621937</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131809042</v>
+        <v>131806457</v>
       </c>
       <c r="B120" t="n">
         <v>79397</v>
@@ -13536,13 +13532,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>410318</v>
+        <v>410123</v>
       </c>
       <c r="R120" t="n">
-        <v>6741647</v>
+        <v>6741557</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13569,67 +13565,76 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809042</t>
+          <t>https://artportalen.se/Sighting/131806457</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806354</v>
+        <v>131809042</v>
       </c>
       <c r="B121" t="n">
-        <v>78776</v>
+        <v>79397</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13639,13 +13644,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>410598</v>
+        <v>410318</v>
       </c>
       <c r="R121" t="n">
-        <v>6741624</v>
+        <v>6741647</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13672,51 +13677,42 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806354</t>
+          <t>https://artportalen.se/Sighting/131809042</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131806489</v>
+        <v>131806354</v>
       </c>
       <c r="B122" t="n">
         <v>78776</v>
@@ -13751,10 +13747,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>410191</v>
+        <v>410598</v>
       </c>
       <c r="R122" t="n">
-        <v>6741549</v>
+        <v>6741624</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13786,7 +13782,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13796,12 +13792,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>På torraka med fyra brnadljud</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13827,16 +13818,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806489</t>
+          <t>https://artportalen.se/Sighting/131806354</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131808974</v>
+        <v>131806489</v>
       </c>
       <c r="B123" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13844,40 +13835,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>410339</v>
+        <v>410191</v>
       </c>
       <c r="R123" t="n">
-        <v>6741540</v>
+        <v>6741549</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13904,42 +13892,56 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>På torraka med fyra brnadljud</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808974</t>
+          <t>https://artportalen.se/Sighting/131806489</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131808975</v>
+        <v>131808974</v>
       </c>
       <c r="B124" t="n">
         <v>83358</v>
@@ -13977,10 +13979,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>410579</v>
+        <v>410339</v>
       </c>
       <c r="R124" t="n">
-        <v>6741619</v>
+        <v>6741540</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -14039,13 +14041,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808975</t>
+          <t>https://artportalen.se/Sighting/131808974</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131808976</v>
+        <v>131808975</v>
       </c>
       <c r="B125" t="n">
         <v>83358</v>
@@ -14083,10 +14085,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>410372</v>
+        <v>410579</v>
       </c>
       <c r="R125" t="n">
-        <v>6741606</v>
+        <v>6741619</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -14145,13 +14147,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808976</t>
+          <t>https://artportalen.se/Sighting/131808975</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131808978</v>
+        <v>131808976</v>
       </c>
       <c r="B126" t="n">
         <v>83358</v>
@@ -14189,10 +14191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>410571</v>
+        <v>410372</v>
       </c>
       <c r="R126" t="n">
-        <v>6741621</v>
+        <v>6741606</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -14251,13 +14253,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808978</t>
+          <t>https://artportalen.se/Sighting/131808976</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131808980</v>
+        <v>131808978</v>
       </c>
       <c r="B127" t="n">
         <v>83358</v>
@@ -14295,10 +14297,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>410551</v>
+        <v>410571</v>
       </c>
       <c r="R127" t="n">
-        <v>6741611</v>
+        <v>6741621</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -14357,13 +14359,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808980</t>
+          <t>https://artportalen.se/Sighting/131808978</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131808983</v>
+        <v>131808980</v>
       </c>
       <c r="B128" t="n">
         <v>83358</v>
@@ -14401,10 +14403,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>410580</v>
+        <v>410551</v>
       </c>
       <c r="R128" t="n">
-        <v>6741625</v>
+        <v>6741611</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -14463,38 +14465,38 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131808983</t>
+          <t>https://artportalen.se/Sighting/131808980</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132621915</v>
+        <v>131808983</v>
       </c>
       <c r="B129" t="n">
-        <v>78731</v>
+        <v>83358</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14507,13 +14509,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>410346</v>
+        <v>410580</v>
       </c>
       <c r="R129" t="n">
-        <v>6741646</v>
+        <v>6741625</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14537,12 +14539,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14563,60 +14565,63 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621915</t>
+          <t>https://artportalen.se/Sighting/131808983</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131806458</v>
+        <v>132621915</v>
       </c>
       <c r="B130" t="n">
-        <v>79130</v>
+        <v>78731</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6443</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>410123</v>
+        <v>410346</v>
       </c>
       <c r="R130" t="n">
-        <v>6741558</v>
+        <v>6741646</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14640,22 +14645,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14664,33 +14659,34 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806458</t>
+          <t>https://artportalen.se/Sighting/132621915</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131806456</v>
+        <v>131806458</v>
       </c>
       <c r="B131" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14698,21 +14694,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14793,13 +14789,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806456</t>
+          <t>https://artportalen.se/Sighting/131806458</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131809008</v>
+        <v>131806456</v>
       </c>
       <c r="B132" t="n">
         <v>79992</v>
@@ -14834,13 +14830,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>410253</v>
+        <v>410123</v>
       </c>
       <c r="R132" t="n">
-        <v>6741548</v>
+        <v>6741558</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14867,9 +14863,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14884,24 +14890,24 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809008</t>
+          <t>https://artportalen.se/Sighting/131806456</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132621865</v>
+        <v>131809008</v>
       </c>
       <c r="B133" t="n">
         <v>79992</v>
@@ -14936,13 +14942,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>410608</v>
+        <v>410253</v>
       </c>
       <c r="R133" t="n">
-        <v>6741559</v>
+        <v>6741548</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14966,12 +14972,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14991,19 +14997,19 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621865</t>
+          <t>https://artportalen.se/Sighting/131809008</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132621866</v>
+        <v>132621865</v>
       </c>
       <c r="B134" t="n">
         <v>79992</v>
@@ -15038,10 +15044,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>410320</v>
+        <v>410608</v>
       </c>
       <c r="R134" t="n">
-        <v>6741612</v>
+        <v>6741559</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15093,19 +15099,19 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621866</t>
+          <t>https://artportalen.se/Sighting/132621865</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132621870</v>
+        <v>132621866</v>
       </c>
       <c r="B135" t="n">
         <v>79992</v>
@@ -15140,10 +15146,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>410249</v>
+        <v>410320</v>
       </c>
       <c r="R135" t="n">
-        <v>6741544</v>
+        <v>6741612</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15201,13 +15207,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621870</t>
+          <t>https://artportalen.se/Sighting/132621866</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132621871</v>
+        <v>132621870</v>
       </c>
       <c r="B136" t="n">
         <v>79992</v>
@@ -15242,10 +15248,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>410252</v>
+        <v>410249</v>
       </c>
       <c r="R136" t="n">
-        <v>6741545</v>
+        <v>6741544</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15303,13 +15309,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621871</t>
+          <t>https://artportalen.se/Sighting/132621870</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132621872</v>
+        <v>132621871</v>
       </c>
       <c r="B137" t="n">
         <v>79992</v>
@@ -15344,10 +15350,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>410206</v>
+        <v>410252</v>
       </c>
       <c r="R137" t="n">
-        <v>6741612</v>
+        <v>6741545</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15405,13 +15411,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621872</t>
+          <t>https://artportalen.se/Sighting/132621871</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132621875</v>
+        <v>132621872</v>
       </c>
       <c r="B138" t="n">
         <v>79992</v>
@@ -15446,10 +15452,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>410349</v>
+        <v>410206</v>
       </c>
       <c r="R138" t="n">
-        <v>6741643</v>
+        <v>6741612</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15507,13 +15513,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621875</t>
+          <t>https://artportalen.se/Sighting/132621872</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132621877</v>
+        <v>132621875</v>
       </c>
       <c r="B139" t="n">
         <v>79992</v>
@@ -15548,10 +15554,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>410687</v>
+        <v>410349</v>
       </c>
       <c r="R139" t="n">
-        <v>6741620</v>
+        <v>6741643</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15609,16 +15615,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621877</t>
+          <t>https://artportalen.se/Sighting/132621875</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131806522</v>
+        <v>132621877</v>
       </c>
       <c r="B140" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15626,21 +15632,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15650,13 +15656,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>410192</v>
+        <v>410687</v>
       </c>
       <c r="R140" t="n">
-        <v>6741630</v>
+        <v>6741620</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15680,22 +15686,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15710,24 +15706,24 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806522</t>
+          <t>https://artportalen.se/Sighting/132621877</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131812551</v>
+        <v>131806522</v>
       </c>
       <c r="B141" t="n">
         <v>78377</v>
@@ -15756,22 +15752,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>410589</v>
+        <v>410192</v>
       </c>
       <c r="R141" t="n">
-        <v>6741618</v>
+        <v>6741630</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15798,88 +15791,95 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131812551</t>
+          <t>https://artportalen.se/Sighting/131806522</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131806416</v>
+        <v>131812551</v>
       </c>
       <c r="B142" t="n">
-        <v>57972</v>
+        <v>78377</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>410352</v>
+        <v>410589</v>
       </c>
       <c r="R142" t="n">
-        <v>6741580</v>
+        <v>6741618</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15906,56 +15906,42 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>I torraka</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806416</t>
+          <t>https://artportalen.se/Sighting/131812551</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131806435</v>
+        <v>131806416</v>
       </c>
       <c r="B143" t="n">
         <v>57972</v>
@@ -15995,10 +15981,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>410257</v>
+        <v>410352</v>
       </c>
       <c r="R143" t="n">
-        <v>6741554</v>
+        <v>6741580</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16030,7 +16016,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16040,7 +16026,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>I torraka</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16066,13 +16057,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806435</t>
+          <t>https://artportalen.se/Sighting/131806416</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131806473</v>
+        <v>131806435</v>
       </c>
       <c r="B144" t="n">
         <v>57972</v>
@@ -16112,10 +16103,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>410166</v>
+        <v>410257</v>
       </c>
       <c r="R144" t="n">
-        <v>6741550</v>
+        <v>6741554</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16147,7 +16138,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16157,7 +16148,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16183,33 +16174,33 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806473</t>
+          <t>https://artportalen.se/Sighting/131806435</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131806351</v>
+        <v>131806473</v>
       </c>
       <c r="B145" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -16220,7 +16211,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16229,10 +16220,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>410470</v>
+        <v>410166</v>
       </c>
       <c r="R145" t="n">
-        <v>6741635</v>
+        <v>6741550</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16264,7 +16255,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16274,7 +16265,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16300,13 +16291,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806351</t>
+          <t>https://artportalen.se/Sighting/131806473</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131806369</v>
+        <v>131806351</v>
       </c>
       <c r="B146" t="n">
         <v>57975</v>
@@ -16346,10 +16337,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>410731</v>
+        <v>410470</v>
       </c>
       <c r="R146" t="n">
-        <v>6741576</v>
+        <v>6741635</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16381,7 +16372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16391,7 +16382,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16417,13 +16408,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806369</t>
+          <t>https://artportalen.se/Sighting/131806351</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131806373</v>
+        <v>131806369</v>
       </c>
       <c r="B147" t="n">
         <v>57975</v>
@@ -16463,10 +16454,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>410655</v>
+        <v>410731</v>
       </c>
       <c r="R147" t="n">
-        <v>6741583</v>
+        <v>6741576</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16498,7 +16489,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16508,7 +16499,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16534,13 +16525,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806373</t>
+          <t>https://artportalen.se/Sighting/131806369</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131806384</v>
+        <v>131806373</v>
       </c>
       <c r="B148" t="n">
         <v>57975</v>
@@ -16580,10 +16571,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>410549</v>
+        <v>410655</v>
       </c>
       <c r="R148" t="n">
-        <v>6741560</v>
+        <v>6741583</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16615,7 +16606,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16625,7 +16616,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16651,13 +16642,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806384</t>
+          <t>https://artportalen.se/Sighting/131806373</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131806385</v>
+        <v>131806384</v>
       </c>
       <c r="B149" t="n">
         <v>57975</v>
@@ -16697,10 +16688,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>410544</v>
+        <v>410549</v>
       </c>
       <c r="R149" t="n">
-        <v>6741545</v>
+        <v>6741560</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16732,7 +16723,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16742,7 +16733,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16768,13 +16759,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806385</t>
+          <t>https://artportalen.se/Sighting/131806384</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131806391</v>
+        <v>131806385</v>
       </c>
       <c r="B150" t="n">
         <v>57975</v>
@@ -16814,10 +16805,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>410512</v>
+        <v>410544</v>
       </c>
       <c r="R150" t="n">
-        <v>6741584</v>
+        <v>6741545</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16849,7 +16840,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16859,7 +16850,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16885,13 +16876,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806391</t>
+          <t>https://artportalen.se/Sighting/131806385</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131806395</v>
+        <v>131806391</v>
       </c>
       <c r="B151" t="n">
         <v>57975</v>
@@ -16931,10 +16922,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>410502</v>
+        <v>410512</v>
       </c>
       <c r="R151" t="n">
-        <v>6741573</v>
+        <v>6741584</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16966,7 +16957,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16976,7 +16967,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17002,13 +16993,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806395</t>
+          <t>https://artportalen.se/Sighting/131806391</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131806396</v>
+        <v>131806395</v>
       </c>
       <c r="B152" t="n">
         <v>57975</v>
@@ -17039,7 +17030,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17048,10 +17039,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>410485</v>
+        <v>410502</v>
       </c>
       <c r="R152" t="n">
-        <v>6741564</v>
+        <v>6741573</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17083,7 +17074,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17093,12 +17084,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17124,13 +17110,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806396</t>
+          <t>https://artportalen.se/Sighting/131806395</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131806397</v>
+        <v>131806396</v>
       </c>
       <c r="B153" t="n">
         <v>57975</v>
@@ -17161,7 +17147,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17170,10 +17156,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>410490</v>
+        <v>410485</v>
       </c>
       <c r="R153" t="n">
-        <v>6741572</v>
+        <v>6741564</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17218,6 +17204,11 @@
           <t>11:56</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -17241,13 +17232,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806397</t>
+          <t>https://artportalen.se/Sighting/131806396</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131806399</v>
+        <v>131806397</v>
       </c>
       <c r="B154" t="n">
         <v>57975</v>
@@ -17287,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>410482</v>
+        <v>410490</v>
       </c>
       <c r="R154" t="n">
-        <v>6741564</v>
+        <v>6741572</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17322,7 +17313,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17332,12 +17323,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17363,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806399</t>
+          <t>https://artportalen.se/Sighting/131806397</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131806407</v>
+        <v>131806399</v>
       </c>
       <c r="B155" t="n">
         <v>57975</v>
@@ -17409,10 +17395,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>410432</v>
+        <v>410482</v>
       </c>
       <c r="R155" t="n">
-        <v>6741569</v>
+        <v>6741564</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17444,7 +17430,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17454,12 +17440,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Skalad smågran</t>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17485,13 +17471,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806407</t>
+          <t>https://artportalen.se/Sighting/131806399</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131806408</v>
+        <v>131806407</v>
       </c>
       <c r="B156" t="n">
         <v>57975</v>
@@ -17522,7 +17508,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17531,10 +17517,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>410427</v>
+        <v>410432</v>
       </c>
       <c r="R156" t="n">
-        <v>6741574</v>
+        <v>6741569</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17566,7 +17552,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17576,12 +17562,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Skalad smågran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17607,13 +17593,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806408</t>
+          <t>https://artportalen.se/Sighting/131806407</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131806434</v>
+        <v>131806408</v>
       </c>
       <c r="B157" t="n">
         <v>57975</v>
@@ -17644,7 +17630,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17653,10 +17639,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>410257</v>
+        <v>410427</v>
       </c>
       <c r="R157" t="n">
-        <v>6741554</v>
+        <v>6741574</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17688,7 +17674,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17698,7 +17684,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17724,13 +17715,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806434</t>
+          <t>https://artportalen.se/Sighting/131806408</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131806440</v>
+        <v>131806434</v>
       </c>
       <c r="B158" t="n">
         <v>57975</v>
@@ -17770,10 +17761,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>410216</v>
+        <v>410257</v>
       </c>
       <c r="R158" t="n">
-        <v>6741551</v>
+        <v>6741554</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17805,7 +17796,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17815,7 +17806,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17841,13 +17832,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806440</t>
+          <t>https://artportalen.se/Sighting/131806434</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131806449</v>
+        <v>131806440</v>
       </c>
       <c r="B159" t="n">
         <v>57975</v>
@@ -17878,7 +17869,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17887,10 +17878,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>410117</v>
+        <v>410216</v>
       </c>
       <c r="R159" t="n">
-        <v>6741596</v>
+        <v>6741551</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17922,7 +17913,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17932,12 +17923,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17963,13 +17949,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806449</t>
+          <t>https://artportalen.se/Sighting/131806440</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131806478</v>
+        <v>131806449</v>
       </c>
       <c r="B160" t="n">
         <v>57975</v>
@@ -18000,7 +17986,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18009,10 +17995,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>410174</v>
+        <v>410117</v>
       </c>
       <c r="R160" t="n">
-        <v>6741529</v>
+        <v>6741596</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18044,7 +18030,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18054,7 +18040,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18080,13 +18071,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806478</t>
+          <t>https://artportalen.se/Sighting/131806449</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131806482</v>
+        <v>131806478</v>
       </c>
       <c r="B161" t="n">
         <v>57975</v>
@@ -18117,7 +18108,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18126,10 +18117,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>410178</v>
+        <v>410174</v>
       </c>
       <c r="R161" t="n">
-        <v>6741516</v>
+        <v>6741529</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18161,7 +18152,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18171,7 +18162,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18197,13 +18188,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806482</t>
+          <t>https://artportalen.se/Sighting/131806478</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131806491</v>
+        <v>131806482</v>
       </c>
       <c r="B162" t="n">
         <v>57975</v>
@@ -18234,7 +18225,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18243,10 +18234,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>410195</v>
+        <v>410178</v>
       </c>
       <c r="R162" t="n">
-        <v>6741554</v>
+        <v>6741516</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18278,7 +18269,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18288,7 +18279,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18314,13 +18305,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806491</t>
+          <t>https://artportalen.se/Sighting/131806482</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131806494</v>
+        <v>131806491</v>
       </c>
       <c r="B163" t="n">
         <v>57975</v>
@@ -18360,10 +18351,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>410192</v>
+        <v>410195</v>
       </c>
       <c r="R163" t="n">
-        <v>6741561</v>
+        <v>6741554</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18395,7 +18386,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18405,7 +18396,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18431,13 +18422,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806494</t>
+          <t>https://artportalen.se/Sighting/131806491</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131806497</v>
+        <v>131806494</v>
       </c>
       <c r="B164" t="n">
         <v>57975</v>
@@ -18468,7 +18459,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18477,10 +18468,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>410197</v>
+        <v>410192</v>
       </c>
       <c r="R164" t="n">
-        <v>6741577</v>
+        <v>6741561</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18512,7 +18503,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18522,7 +18513,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18548,13 +18539,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806497</t>
+          <t>https://artportalen.se/Sighting/131806494</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131806507</v>
+        <v>131806497</v>
       </c>
       <c r="B165" t="n">
         <v>57975</v>
@@ -18585,7 +18576,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -18594,10 +18585,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>410221</v>
+        <v>410197</v>
       </c>
       <c r="R165" t="n">
-        <v>6741596</v>
+        <v>6741577</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18629,7 +18620,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18639,7 +18630,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18665,13 +18656,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806507</t>
+          <t>https://artportalen.se/Sighting/131806497</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>131809020</v>
+        <v>131806507</v>
       </c>
       <c r="B166" t="n">
         <v>57975</v>
@@ -18700,19 +18691,24 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>410369</v>
+        <v>410221</v>
       </c>
       <c r="R166" t="n">
-        <v>6741611</v>
+        <v>6741596</v>
       </c>
       <c r="S166" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18739,9 +18735,19 @@
           <t>2026-03-20</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18756,24 +18762,24 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809020</t>
+          <t>https://artportalen.se/Sighting/131806507</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131809023</v>
+        <v>131809020</v>
       </c>
       <c r="B167" t="n">
         <v>57975</v>
@@ -18808,10 +18814,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>410476</v>
+        <v>410369</v>
       </c>
       <c r="R167" t="n">
-        <v>6741605</v>
+        <v>6741611</v>
       </c>
       <c r="S167" t="n">
         <v>20</v>
@@ -18869,13 +18875,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809023</t>
+          <t>https://artportalen.se/Sighting/131809020</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131809026</v>
+        <v>131809023</v>
       </c>
       <c r="B168" t="n">
         <v>57975</v>
@@ -18904,24 +18910,16 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>410354</v>
+        <v>410476</v>
       </c>
       <c r="R168" t="n">
-        <v>6741532</v>
+        <v>6741605</v>
       </c>
       <c r="S168" t="n">
         <v>20</v>
@@ -18956,11 +18954,6 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -18984,13 +18977,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809026</t>
+          <t>https://artportalen.se/Sighting/131809023</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131809027</v>
+        <v>131809026</v>
       </c>
       <c r="B169" t="n">
         <v>57975</v>
@@ -19033,10 +19026,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>410356</v>
+        <v>410354</v>
       </c>
       <c r="R169" t="n">
-        <v>6741540</v>
+        <v>6741532</v>
       </c>
       <c r="S169" t="n">
         <v>20</v>
@@ -19099,13 +19092,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809027</t>
+          <t>https://artportalen.se/Sighting/131809026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131809028</v>
+        <v>131809027</v>
       </c>
       <c r="B170" t="n">
         <v>57975</v>
@@ -19148,10 +19141,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>410423</v>
+        <v>410356</v>
       </c>
       <c r="R170" t="n">
-        <v>6741606</v>
+        <v>6741540</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -19214,13 +19207,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809028</t>
+          <t>https://artportalen.se/Sighting/131809027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131809031</v>
+        <v>131809028</v>
       </c>
       <c r="B171" t="n">
         <v>57975</v>
@@ -19263,10 +19256,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>410355</v>
+        <v>410423</v>
       </c>
       <c r="R171" t="n">
-        <v>6741540</v>
+        <v>6741606</v>
       </c>
       <c r="S171" t="n">
         <v>20</v>
@@ -19329,13 +19322,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809031</t>
+          <t>https://artportalen.se/Sighting/131809028</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131809034</v>
+        <v>131809031</v>
       </c>
       <c r="B172" t="n">
         <v>57975</v>
@@ -19378,10 +19371,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>410416</v>
+        <v>410355</v>
       </c>
       <c r="R172" t="n">
-        <v>6741600</v>
+        <v>6741540</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -19444,13 +19437,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809034</t>
+          <t>https://artportalen.se/Sighting/131809031</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131809035</v>
+        <v>131809034</v>
       </c>
       <c r="B173" t="n">
         <v>57975</v>
@@ -19493,10 +19486,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>410502</v>
+        <v>410416</v>
       </c>
       <c r="R173" t="n">
-        <v>6741621</v>
+        <v>6741600</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -19559,59 +19552,62 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131809035</t>
+          <t>https://artportalen.se/Sighting/131809034</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131806499</v>
+        <v>131809035</v>
       </c>
       <c r="B174" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>410179</v>
+        <v>410502</v>
       </c>
       <c r="R174" t="n">
-        <v>6741569</v>
+        <v>6741621</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19638,19 +19634,14 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19665,24 +19656,24 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806499</t>
+          <t>https://artportalen.se/Sighting/131809035</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131806514</v>
+        <v>131806499</v>
       </c>
       <c r="B175" t="n">
         <v>57162</v>
@@ -19722,10 +19713,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>410257</v>
+        <v>410179</v>
       </c>
       <c r="R175" t="n">
-        <v>6741601</v>
+        <v>6741569</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19757,7 +19748,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19767,7 +19758,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19793,13 +19784,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806514</t>
+          <t>https://artportalen.se/Sighting/131806499</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>132621893</v>
+        <v>131806514</v>
       </c>
       <c r="B176" t="n">
         <v>57162</v>
@@ -19827,9 +19818,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19838,13 +19830,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>410712</v>
+        <v>410257</v>
       </c>
       <c r="R176" t="n">
-        <v>6741559</v>
+        <v>6741601</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19868,12 +19860,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19888,27 +19890,27 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621893</t>
+          <t>https://artportalen.se/Sighting/131806514</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131806498</v>
+        <v>132621893</v>
       </c>
       <c r="B177" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19916,27 +19918,26 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19945,13 +19946,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>410197</v>
+        <v>410712</v>
       </c>
       <c r="R177" t="n">
-        <v>6741577</v>
+        <v>6741559</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19975,22 +19976,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20005,55 +19996,55 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806498</t>
+          <t>https://artportalen.se/Sighting/132621893</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131806358</v>
+        <v>131806498</v>
       </c>
       <c r="B178" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -20062,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>410709</v>
+        <v>410197</v>
       </c>
       <c r="R178" t="n">
-        <v>6741602</v>
+        <v>6741577</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20097,7 +20088,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20107,7 +20098,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20133,13 +20124,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806358</t>
+          <t>https://artportalen.se/Sighting/131806498</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131806441</v>
+        <v>131806358</v>
       </c>
       <c r="B179" t="n">
         <v>58136</v>
@@ -20167,9 +20158,10 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -20178,10 +20170,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>410179</v>
+        <v>410709</v>
       </c>
       <c r="R179" t="n">
-        <v>6741551</v>
+        <v>6741602</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20213,7 +20205,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20223,7 +20215,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20249,44 +20241,43 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806441</t>
+          <t>https://artportalen.se/Sighting/131806358</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131806429</v>
+        <v>131806441</v>
       </c>
       <c r="B180" t="n">
-        <v>8460</v>
+        <v>58136</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20295,10 +20286,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>410279</v>
+        <v>410179</v>
       </c>
       <c r="R180" t="n">
-        <v>6741504</v>
+        <v>6741551</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20330,7 +20321,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20340,7 +20331,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20366,13 +20357,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806429</t>
+          <t>https://artportalen.se/Sighting/131806441</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131806444</v>
+        <v>131806429</v>
       </c>
       <c r="B181" t="n">
         <v>8460</v>
@@ -20412,10 +20403,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>410225</v>
+        <v>410279</v>
       </c>
       <c r="R181" t="n">
-        <v>6741556</v>
+        <v>6741504</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20447,7 +20438,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20457,7 +20448,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20483,13 +20474,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806444</t>
+          <t>https://artportalen.se/Sighting/131806429</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131806450</v>
+        <v>131806444</v>
       </c>
       <c r="B182" t="n">
         <v>8460</v>
@@ -20529,10 +20520,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>410130</v>
+        <v>410225</v>
       </c>
       <c r="R182" t="n">
-        <v>6741614</v>
+        <v>6741556</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20564,7 +20555,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20574,7 +20565,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20600,13 +20591,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806450</t>
+          <t>https://artportalen.se/Sighting/131806444</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131806493</v>
+        <v>131806450</v>
       </c>
       <c r="B183" t="n">
         <v>8460</v>
@@ -20646,10 +20637,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>410203</v>
+        <v>410130</v>
       </c>
       <c r="R183" t="n">
-        <v>6741568</v>
+        <v>6741614</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20681,7 +20672,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20691,7 +20682,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20717,13 +20708,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806493</t>
+          <t>https://artportalen.se/Sighting/131806450</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>131806519</v>
+        <v>131806493</v>
       </c>
       <c r="B184" t="n">
         <v>8460</v>
@@ -20763,10 +20754,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>410240</v>
+        <v>410203</v>
       </c>
       <c r="R184" t="n">
-        <v>6741632</v>
+        <v>6741568</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20798,7 +20789,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20808,7 +20799,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20834,16 +20825,16 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806519</t>
+          <t>https://artportalen.se/Sighting/131806493</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>131806370</v>
+        <v>131806519</v>
       </c>
       <c r="B185" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20851,21 +20842,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20880,10 +20871,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>410677</v>
+        <v>410240</v>
       </c>
       <c r="R185" t="n">
-        <v>6741573</v>
+        <v>6741632</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20915,7 +20906,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20925,7 +20916,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20951,54 +20942,59 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806370</t>
+          <t>https://artportalen.se/Sighting/131806519</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>132611050</v>
+        <v>131806370</v>
       </c>
       <c r="B186" t="n">
-        <v>56706</v>
+        <v>8449</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>410504</v>
+        <v>410677</v>
       </c>
       <c r="R186" t="n">
-        <v>6741536</v>
+        <v>6741573</v>
       </c>
       <c r="S186" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21022,12 +21018,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21042,27 +21048,27 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132611050</t>
+          <t>https://artportalen.se/Sighting/131806370</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>132611057</v>
+        <v>132611050</v>
       </c>
       <c r="B187" t="n">
-        <v>79131</v>
+        <v>56706</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21070,21 +21076,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>228912</v>
+        <v>206046</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21094,10 +21100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>410329</v>
+        <v>410504</v>
       </c>
       <c r="R187" t="n">
-        <v>6741593</v>
+        <v>6741536</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -21155,13 +21161,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132611057</t>
+          <t>https://artportalen.se/Sighting/132611050</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>132611058</v>
+        <v>132611057</v>
       </c>
       <c r="B188" t="n">
         <v>79131</v>
@@ -21196,10 +21202,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>410279</v>
+        <v>410329</v>
       </c>
       <c r="R188" t="n">
-        <v>6741644</v>
+        <v>6741593</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -21257,13 +21263,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132611058</t>
+          <t>https://artportalen.se/Sighting/132611057</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>132621900</v>
+        <v>132611058</v>
       </c>
       <c r="B189" t="n">
         <v>79131</v>
@@ -21298,13 +21304,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>410323</v>
+        <v>410279</v>
       </c>
       <c r="R189" t="n">
-        <v>6741612</v>
+        <v>6741644</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21348,27 +21354,27 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Joakim Karlsson, Moa Björnberg Dillner, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621900</t>
+          <t>https://artportalen.se/Sighting/132611058</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>70327925</v>
+        <v>132621900</v>
       </c>
       <c r="B190" t="n">
-        <v>79917</v>
+        <v>79131</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21376,21 +21382,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21400,13 +21406,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>410671</v>
+        <v>410323</v>
       </c>
       <c r="R190" t="n">
-        <v>6741622</v>
+        <v>6741612</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21430,12 +21436,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21450,27 +21456,27 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70327925</t>
+          <t>https://artportalen.se/Sighting/132621900</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>131806346</v>
+        <v>70327925</v>
       </c>
       <c r="B191" t="n">
-        <v>79963</v>
+        <v>79917</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21502,10 +21508,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>410348</v>
+        <v>410671</v>
       </c>
       <c r="R191" t="n">
-        <v>6741643</v>
+        <v>6741622</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21532,22 +21538,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2017-07-19</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21562,24 +21558,24 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806346</t>
+          <t>https://artportalen.se/Sighting/70327925</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>131806376</v>
+        <v>131806346</v>
       </c>
       <c r="B192" t="n">
         <v>79963</v>
@@ -21614,10 +21610,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>410612</v>
+        <v>410348</v>
       </c>
       <c r="R192" t="n">
-        <v>6741582</v>
+        <v>6741643</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21649,7 +21645,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21659,7 +21655,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21685,13 +21681,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806376</t>
+          <t>https://artportalen.se/Sighting/131806346</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>131806463</v>
+        <v>131806376</v>
       </c>
       <c r="B193" t="n">
         <v>79963</v>
@@ -21726,10 +21722,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>410119</v>
+        <v>410612</v>
       </c>
       <c r="R193" t="n">
-        <v>6741530</v>
+        <v>6741582</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21761,7 +21757,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21771,7 +21767,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21797,13 +21793,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806463</t>
+          <t>https://artportalen.se/Sighting/131806376</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>131806466</v>
+        <v>131806463</v>
       </c>
       <c r="B194" t="n">
         <v>79963</v>
@@ -21838,10 +21834,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>410128</v>
+        <v>410119</v>
       </c>
       <c r="R194" t="n">
-        <v>6741527</v>
+        <v>6741530</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21873,7 +21869,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21883,7 +21879,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21909,13 +21905,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806466</t>
+          <t>https://artportalen.se/Sighting/131806463</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>132621878</v>
+        <v>131806466</v>
       </c>
       <c r="B195" t="n">
         <v>79963</v>
@@ -21950,13 +21946,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>410320</v>
+        <v>410128</v>
       </c>
       <c r="R195" t="n">
-        <v>6741612</v>
+        <v>6741527</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21980,12 +21976,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22000,24 +22006,24 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621878</t>
+          <t>https://artportalen.se/Sighting/131806466</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>132621885</v>
+        <v>132621878</v>
       </c>
       <c r="B196" t="n">
         <v>79963</v>
@@ -22052,10 +22058,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>410220</v>
+        <v>410320</v>
       </c>
       <c r="R196" t="n">
-        <v>6741586</v>
+        <v>6741612</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -22113,38 +22119,38 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132621885</t>
+          <t>https://artportalen.se/Sighting/132621878</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>131806362</v>
+        <v>132621885</v>
       </c>
       <c r="B197" t="n">
-        <v>79373</v>
+        <v>79963</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22154,13 +22160,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>410754</v>
+        <v>410220</v>
       </c>
       <c r="R197" t="n">
-        <v>6741593</v>
+        <v>6741586</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22184,22 +22190,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22214,24 +22210,24 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Ossian Tulin, Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806362</t>
+          <t>https://artportalen.se/Sighting/132621885</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>131806365</v>
+        <v>131806362</v>
       </c>
       <c r="B198" t="n">
         <v>79373</v>
@@ -22266,10 +22262,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>410757</v>
+        <v>410754</v>
       </c>
       <c r="R198" t="n">
-        <v>6741575</v>
+        <v>6741593</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22301,7 +22297,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22311,7 +22307,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22337,56 +22333,51 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806365</t>
+          <t>https://artportalen.se/Sighting/131806362</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>131806364</v>
+        <v>131806365</v>
       </c>
       <c r="B199" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Björnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>410774</v>
+        <v>410757</v>
       </c>
       <c r="R199" t="n">
-        <v>6741570</v>
+        <v>6741575</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22418,7 +22409,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22428,12 +22419,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Skalad smågran</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22459,44 +22445,44 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131806364</t>
+          <t>https://artportalen.se/Sighting/131806365</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>131806363</v>
+        <v>131806364</v>
       </c>
       <c r="B200" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22505,10 +22491,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>410766</v>
+        <v>410774</v>
       </c>
       <c r="R200" t="n">
-        <v>6741592</v>
+        <v>6741570</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22553,6 +22539,11 @@
           <t>12:26</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Skalad smågran</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -22575,6 +22566,123 @@
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131806364</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>131806363</v>
+      </c>
+      <c r="B201" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Björnåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>410766</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6741592</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131806363</t>
         </is>
@@ -22781,6 +22889,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
